--- a/products.xlsx
+++ b/products.xlsx
@@ -509,11 +509,7 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>chua biet</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>bf245d34d7bb3918cb3e74514207c3dc</t>
@@ -583,9 +579,6 @@
           <t>Liên hệ</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>https://</t>
@@ -596,8 +589,6 @@
           <t>https://via.placeholder.com/400x300?text=No+Image</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>d77f60178754eb2d9e9cc9affc1539e8</t>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,128 +470,6 @@
       <c r="K1" t="inlineStr">
         <is>
           <t>hash</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Tên mới</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>bf245d34d7bb3918cb3e74514207c3dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Tên mới</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>biet roi</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>b03edff1019f544b1dcf08f816e90c9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tên mới</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Liên hệ</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>https://via.placeholder.com/400x300?text=No+Image</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>
       </c>
     </row>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,998 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>₫49.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24 </t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>shopee_48200038200</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>₫109.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56 </t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57450548196?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>shopee_57450548196</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>113eb535211dc5576ce1f369536e321f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>₫86.400</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">573 </t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>shopee_23611804472</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>₫250.000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>shopee_40176467388</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>10k+</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19,5%</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>shopee_24288149456</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>₫172.000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2k+</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>33,5%</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>shopee_47051514276</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>₫259.424</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 </t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43054873326?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>shopee_43054873326</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>₫187.000</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 </t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>25,5%</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>shopee_55054542761</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>₫90.000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>103,5%</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>shopee_40423252463</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35 </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>31,5%</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>shopee_26688092638</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>₫98.000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">343 </t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>shopee_25964311284</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>100k+</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>shopee_25123423072</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>₫149.000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189 </t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>18,5%</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>shopee_45358208563</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354 </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>58,5%</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>shopee_25420035796</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>₫70.000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>27,5%</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>shopee_54407073060</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>a99d221105436bf0694d2756ca9de059</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>70k+</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>11,5%</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>shopee_24389484524</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>386b9af5df5a395ff6886d6c5b9821e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>53,5%</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>shopee_51401292730</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>₫1.599.000</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>20%</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>4k+</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>13,5%</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>shopee_40012750336</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Shopee</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Giấy ăn rút Topgia thùng 40 gói đa sắc cao cấp 240 tờ 4 lớp, dập vân 4D, mềm mịn, thấm hút tốt</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>₫95.000</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>3k+</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>14,5%</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57860887539?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp0p9xne07ikdf.webp</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>shopee_57860887539</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>f9639d41fbcd6e80bee0e8864b3f4099</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/products.xlsx
+++ b/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,44 +481,47 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
+          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>₫49.000</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>₫189.000</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">24 </t>
+          <t xml:space="preserve">35 </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>shopee_48200038200</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>shopee_26688092638</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
+          <t>20e232b6634d40cd43b0a947914769d6</t>
         </is>
       </c>
     </row>
@@ -530,44 +533,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
+          <t>Giấy ăn rút Topgia thùng 40 gói đa sắc cao cấp 240 tờ 4 lớp, dập vân 4D, mềm mịn, thấm hút tốt</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>₫109.000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>₫95.000</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56 </t>
+          <t>3k+</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57450548196?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57860887539?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp0p9xne07ikdf.webp</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>shopee_57450548196</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>shopee_57860887539</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>113eb535211dc5576ce1f369536e321f</t>
+          <t>f9639d41fbcd6e80bee0e8864b3f4099</t>
         </is>
       </c>
     </row>
@@ -579,44 +585,47 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
+          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>₫86.400</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>₫159.000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">573 </t>
+          <t>100k+</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>shopee_23611804472</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>shopee_25123423072</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
+          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
         </is>
       </c>
     </row>
@@ -628,44 +637,47 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
+          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>₫250.000</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>₫334.000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2k+</t>
+          <t>10k+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>shopee_40176467388</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>shopee_24288149456</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>20c8bfa466ba333c337b5df598008b75</t>
+          <t>b09e4c6f894042c3f2551d25cdee8335</t>
         </is>
       </c>
     </row>
@@ -677,48 +689,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Combo Sữa tắm gội nam 3in1 &amp; Sữa rửa mặt nam 100ml &amp; Dung dịch vệ sinh 100ml &amp; Nước hoa nam RHYS MAN</t>
+          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>₫334.000</t>
+          <t>₫1.599.000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10k+</t>
+          <t>4k+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24288149456?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mq6i0q75gjkef1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>shopee_24288149456</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>shopee_40012750336</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>b09e4c6f894042c3f2551d25cdee8335</t>
+          <t>3d93b1393727dc3578c2df28b475e423</t>
         </is>
       </c>
     </row>
@@ -730,40 +741,47 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
+          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>₫85.000</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>70k+</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>shopee_53401541671</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>shopee_24389484524</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>aef6c3542d96a164f2f808809d3f5b09</t>
+          <t>386b9af5df5a395ff6886d6c5b9821e3</t>
         </is>
       </c>
     </row>
@@ -775,15 +793,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
+          <t>[MUA 1 TẶNG 1] Kem chống nắng Vichy Emulsion Dry Touch SPF50+ 50ml</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>₫172.000</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>₫250.000</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>2k+</t>
@@ -796,23 +813,22 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40176467388?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhz06xkizl6t4b.webp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>shopee_47051514276</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>shopee_40176467388</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>e534da14d58fabb5a795457bc5e0648f</t>
+          <t>20c8bfa466ba333c337b5df598008b75</t>
         </is>
       </c>
     </row>
@@ -824,44 +840,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
+          <t>[MUA 1 TẶNG 1] Nước tẩy trang Loreal Tím 400ml L'Oreal Revitalift HA Hyaluronic Acid Giảm Dầu Mụn, Cấp Ẩm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>₫259.424</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>₫172.000</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 </t>
+          <t>2k+</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/43054873326?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/47051514276?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mhyvdhqcrev4c1.webp</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>shopee_43054873326</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
+          <t>shopee_47051514276</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
+          <t>e534da14d58fabb5a795457bc5e0648f</t>
         </is>
       </c>
     </row>
@@ -873,44 +887,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
+          <t>Túi Đựng Bút Sức Chứa Lớn Đa Năng Họa Tiết Dễ Thương Cho Học Sinh</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>₫187.000</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>₫86.400</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 </t>
+          <t xml:space="preserve">573 </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/23611804472?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-22120-lmjtm8gjj6kv59.webp</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>shopee_55054542761</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>shopee_23611804472</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>5f34e9db093b79d1979ce644f78054b1</t>
+          <t>5a8f123aab39a7ee3abc4b783a4ee9c5</t>
         </is>
       </c>
     </row>
@@ -922,40 +934,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
+          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>₫90.000</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>₫160.000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">354 </t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>103,5%</t>
+          <t>58,5%</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>shopee_40423252463</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>shopee_25420035796</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
+          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
         </is>
       </c>
     </row>
@@ -967,48 +981,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quạt Điều Hòa Phun Sương Mini Wameli WA-99 Dung Tích 500ml 2 Tốc Độ Gió 3 Chế Độ Phun Sương, Cổng Usb Tiện Lợi</t>
+          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>₫189.000</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>50%</t>
+          <t>₫98.000</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">35 </t>
+          <t xml:space="preserve">343 </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/26688092638?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ras8-mbhwr22bjkn816.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>shopee_26688092638</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>shopee_25964311284</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>20e232b6634d40cd43b0a947914769d6</t>
+          <t>2b2611b2a0080242b5b4208e371f4726</t>
         </is>
       </c>
     </row>
@@ -1020,44 +1028,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bọt đánh răng trẻ em cao cấp Orgakids an toàn cho bé làm sạch khoang miệng loại bỏ mảng bám dễ dàng lọ 100ml</t>
+          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>₫98.000</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>₫149.000</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">343 </t>
+          <t xml:space="preserve">189 </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25964311284?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7r98o-lryj7d6v9z2cc2.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>shopee_25964311284</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>shopee_45358208563</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2b2611b2a0080242b5b4208e371f4726</t>
+          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
         </is>
       </c>
     </row>
@@ -1069,48 +1075,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tai Nghe Bluetooth Không Dây AT5 Pro v5.3 Chạm Cảm Ứng, Âm Thanh Hay Có Mic</t>
+          <t>(bán buôn) F5, 20000 mAh sạc kho báu, đi kèm với 4 dây sạc có thể tháo rời, sạc nhanh 25W.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>₫159.000</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>41%</t>
+          <t>₫109.000</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100k+</t>
+          <t xml:space="preserve">56 </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25123423072?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/57450548196?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mku5h3pou6fa8d.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mggnqnp81gy13f.webp</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>shopee_25123423072</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>shopee_57450548196</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>b3069fd70bc4376a9e159dbdae54e01f</t>
+          <t>113eb535211dc5576ce1f369536e321f</t>
         </is>
       </c>
     </row>
@@ -1122,44 +1122,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>(Loại 1) 2026 Quạt cầm tay mini pin 3000mah 5 cấp độ, sạc pin tiện dụng, nhỏ gọn</t>
+          <t>(Wholesale) pro6, tai nghe Bluetooth không dây, không thấm nước, giảm tiếng ồn, tai nghe thể thao</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>₫149.000</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>₫49.000</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">189 </t>
+          <t xml:space="preserve">24 </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/45358208563?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/48200038200?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mnhe3nlle9dy06.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mg6c2y54rnk997.webp</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>shopee_45358208563</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>shopee_48200038200</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>f5e6a233b2fdb9aa51eac6109af0844e</t>
+          <t>db2b85f0d5e40a41400e4929b228f7ff</t>
         </is>
       </c>
     </row>
@@ -1171,44 +1169,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Trà Táo Hoàng Kỳ điều khí, bổ sung khí cho người thường xuyên thức khuya, da vàng, kém sắc</t>
+          <t>Combo 2 Can Nước Xả Vải Comfort Cho Da Nhạy Cảm 3.8L Tiết Kiệm Mềm Sợi Vải Cho Bé Và Gia Đình</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>₫160.000</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>₫187.000</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">354 </t>
+          <t xml:space="preserve">14 </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/25420035796?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/55054542761?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134201-7r98o-lzp4f8ldjuld45.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mjatub2um03q23.webp</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>shopee_25420035796</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>shopee_55054542761</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>03a8e5b5ddee47c44de0744d2fb1c716</t>
+          <t>5f34e9db093b79d1979ce644f78054b1</t>
         </is>
       </c>
     </row>
@@ -1220,40 +1216,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
+          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>₫70.000</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
+          <t>₫356.000</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6 </t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>shopee_54407073060</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>shopee_51401292730</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>a99d221105436bf0694d2756ca9de059</t>
+          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
         </is>
       </c>
     </row>
@@ -1265,48 +1263,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sốt Chấm CayTeDai x1 CAY VỪA - Sốt Muối Chấm Lâm Vlog Cay Tê Dại x1</t>
+          <t>Ô 8-Bone Titan Bạc Cao Su Ba Mặt Tự Động Ô Chống Nắng Tấm Che Nắng Ô Ra</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>₫85.000</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>9%</t>
+          <t>₫259.424</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>70k+</t>
+          <t xml:space="preserve">2 </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/24389484524?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/43054873326?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-7ra0g-m9z9tckp4vtme8.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/cn-11134207-7ras8-mb40znwnno4h9b.webp</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>shopee_24389484524</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>shopee_43054873326</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>386b9af5df5a395ff6886d6c5b9821e3</t>
+          <t>66275ceb00669c44fdd4d3378bb2a4dc</t>
         </is>
       </c>
     </row>
@@ -1318,44 +1310,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20000 mAh điện thoại di động sạc nhanh bốn dây một màn hình kỹ thuật số thông minh dây buộc di động đi lại dây miễn phí</t>
+          <t>Quạt cầm tay mini sạc USB – gọn nhẹ, êm – mang đi học/đi làm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>₫356.000</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6 </t>
+          <t>₫90.000</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>103,5%</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/51401292730?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/40423252463?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh09q5nypfd5b0.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mflfjegr3216dc.webp</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>shopee_51401292730</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
+          <t>shopee_40423252463</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2a9e15558dc4738eceabb3d0934ed7dd</t>
+          <t>fb297618a8fa2d6c5b74c6833b0c8748</t>
         </is>
       </c>
     </row>
@@ -1367,48 +1352,37 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Flycam K812 Pro Max, Máy Bay Điều Khiển Có Tay Cầm Màn Hình, Drone Định Vị GPS Tự Động Quay Về</t>
+          <t>Sạc siêu nhanh, pin dự phòng 20000mAh, dung lượng lớn, tích hợp 4 cáp sạc nhanh</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>₫1.599.000</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>20%</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>4k+</t>
+          <t>₫356.000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/40012750336?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/53401541671?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mh8gr3tozpjc41.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-820l4-mgq7eazki32n3d.webp</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>shopee_40012750336</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>shopee_53401541671</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3d93b1393727dc3578c2df28b475e423</t>
+          <t>aef6c3542d96a164f2f808809d3f5b09</t>
         </is>
       </c>
     </row>
@@ -1420,48 +1394,74 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Giấy ăn rút Topgia thùng 40 gói đa sắc cao cấp 240 tờ 4 lớp, dập vân 4D, mềm mịn, thấm hút tốt</t>
+          <t>Combo 3-5-10 Sét 3 Cuộn Túi Rác Tự Phân Hủy - An Lành 55*65cm - Gia Dụng Sumo 12 -</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>₫95.000</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>48%</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>3k+</t>
+          <t>₫70.000</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://affiliate.shopee.vn/offer/product_offer/57860887539?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
+          <t>https://affiliate.shopee.vn/offer/product_offer/54407073060?trace=%7B%22trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22list_type%22%3A100%2C%22exp_group_ids%22%3A%5B646439%2C473578%2C447104%2C628625%2C516441%2C688356%2C447311%2C568974%5D%2C%22root_trace_id%22%3A%220.JxDJSjjD1b.100%22%2C%22root_list_type%22%3A100%7D</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://down-zl-vn.img.susercontent.com/vn-11134207-81ztc-mp0p9xne07ikdf.webp</t>
+          <t>https://down-zl-vn.img.susercontent.com/sg-11134201-82632-mlp6euhqof0va5.webp</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>shopee_57860887539</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>shopee_54407073060</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>f9639d41fbcd6e80bee0e8864b3f4099</t>
+          <t>a99d221105436bf0694d2756ca9de059</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tên mới</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Liên hệ</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>https://via.placeholder.com/400x300?text=No+Image</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>d77f60178754eb2d9e9cc9affc1539e8</t>
         </is>
       </c>
     </row>
